--- a/data/trans_dic/P71_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P71_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,0; 17,44</t>
+          <t>12,08; 17,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,8; 31,63</t>
+          <t>25,22; 31,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,91; 38,2</t>
+          <t>31,08; 38,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 14,59</t>
+          <t>9,41; 14,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,81; 27,28</t>
+          <t>20,99; 27,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,15; 34,35</t>
+          <t>26,93; 34,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,35; 38,3</t>
+          <t>31,08; 38,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,08; 17,53</t>
+          <t>11,88; 17,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,27; 21,5</t>
+          <t>17,08; 21,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,89; 32,01</t>
+          <t>26,85; 31,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,98; 37,31</t>
+          <t>32,25; 37,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,64; 15,52</t>
+          <t>11,67; 15,5</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,11; 19,49</t>
+          <t>14,42; 19,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,14; 38,53</t>
+          <t>32,4; 38,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,99; 37,16</t>
+          <t>30,94; 37,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 12,61</t>
+          <t>4,16; 12,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,32; 29,3</t>
+          <t>23,37; 29,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,6; 38,76</t>
+          <t>32,42; 38,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,28; 38,15</t>
+          <t>31,93; 37,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,13; 16,15</t>
+          <t>12,2; 16,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,65; 23,51</t>
+          <t>19,65; 23,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,32; 37,98</t>
+          <t>33,52; 37,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,5; 36,86</t>
+          <t>32,36; 36,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,76; 13,51</t>
+          <t>7,66; 13,59</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,59; 22,94</t>
+          <t>16,47; 22,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,83; 38,99</t>
+          <t>31,93; 39,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,61; 46,05</t>
+          <t>38,54; 46,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,0; 17,23</t>
+          <t>10,91; 16,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,5; 34,05</t>
+          <t>27,24; 34,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,18; 40,54</t>
+          <t>33,43; 40,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,04; 50,24</t>
+          <t>42,96; 50,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 17,89</t>
+          <t>6,53; 18,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,83; 27,57</t>
+          <t>22,88; 27,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33,59; 38,58</t>
+          <t>33,39; 38,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41,87; 46,95</t>
+          <t>41,78; 47,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,26; 16,03</t>
+          <t>7,89; 16,05</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 23,72</t>
+          <t>18,43; 23,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,42; 26,19</t>
+          <t>20,69; 26,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,07; 27,81</t>
+          <t>22,32; 28,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,6; 17,8</t>
+          <t>12,14; 17,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,22; 32,92</t>
+          <t>26,91; 32,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,97; 27,53</t>
+          <t>22,13; 27,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,99; 31,81</t>
+          <t>25,96; 31,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,79; 37,87</t>
+          <t>16,87; 39,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,73; 27,55</t>
+          <t>23,74; 27,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,22; 26,01</t>
+          <t>22,22; 26,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,98; 29,11</t>
+          <t>24,95; 28,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,81; 28,37</t>
+          <t>15,83; 29,43</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,6; 19,4</t>
+          <t>16,8; 19,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,1; 32,22</t>
+          <t>28,99; 32,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,94; 35,14</t>
+          <t>31,77; 35,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,65; 13,64</t>
+          <t>9,29; 13,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,34; 29,49</t>
+          <t>26,36; 29,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,96; 33,27</t>
+          <t>29,9; 33,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,14; 37,32</t>
+          <t>33,97; 37,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,22; 22,23</t>
+          <t>13,86; 21,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,85; 23,98</t>
+          <t>22,05; 24,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,95; 32,27</t>
+          <t>30,02; 32,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,49; 35,86</t>
+          <t>33,58; 35,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,82; 17,44</t>
+          <t>12,67; 17,28</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82254; 119554</t>
+          <t>82842; 119751</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>173694; 221503</t>
+          <t>176615; 223530</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>205667; 254169</t>
+          <t>206811; 258133</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56983; 90064</t>
+          <t>58071; 90163</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>141302; 185180</t>
+          <t>142535; 185126</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>187893; 237718</t>
+          <t>186372; 236414</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>208444; 254652</t>
+          <t>206678; 255170</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>86160; 125011</t>
+          <t>84682; 127233</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>235665; 293305</t>
+          <t>233075; 290758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>374434; 445749</t>
+          <t>373794; 443614</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>425477; 496354</t>
+          <t>429017; 499943</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>154839; 206454</t>
+          <t>155323; 206250</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>133681; 184658</t>
+          <t>136600; 183634</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>325752; 390558</t>
+          <t>328435; 390370</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>314360; 377033</t>
+          <t>313925; 378984</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60927; 148984</t>
+          <t>49142; 146534</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>221627; 278399</t>
+          <t>222076; 281405</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>333776; 396865</t>
+          <t>331956; 394949</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>334175; 394881</t>
+          <t>330549; 392066</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>115366; 153560</t>
+          <t>115969; 153218</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>372989; 446237</t>
+          <t>372894; 443565</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>678832; 773812</t>
+          <t>682816; 770833</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>666165; 755539</t>
+          <t>663199; 750105</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>165551; 288033</t>
+          <t>163393; 289754</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>111459; 154110</t>
+          <t>110641; 154283</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>239912; 293904</t>
+          <t>240680; 295341</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>291498; 347702</t>
+          <t>290974; 348060</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76978; 120629</t>
+          <t>76375; 117753</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>184003; 227763</t>
+          <t>182234; 227707</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>257157; 314151</t>
+          <t>259068; 311437</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>337374; 393864</t>
+          <t>336772; 393484</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54440; 160229</t>
+          <t>58466; 161549</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>306037; 369671</t>
+          <t>306722; 371239</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>513563; 589780</t>
+          <t>510449; 588563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>644321; 722575</t>
+          <t>643005; 729322</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>131733; 255846</t>
+          <t>125974; 256120</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>171054; 219673</t>
+          <t>170691; 220441</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>192222; 246612</t>
+          <t>194837; 246274</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>205802; 259304</t>
+          <t>208081; 261068</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>115586; 163256</t>
+          <t>111344; 158649</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>276746; 334698</t>
+          <t>273669; 333019</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>231078; 289587</t>
+          <t>232744; 288747</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>270968; 331735</t>
+          <t>270746; 331726</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>181973; 410541</t>
+          <t>182900; 425367</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>461047; 535285</t>
+          <t>461321; 533936</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>443013; 518506</t>
+          <t>442873; 520004</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>493399; 575037</t>
+          <t>492717; 569818</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>316363; 567746</t>
+          <t>316729; 589047</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>536405; 626782</t>
+          <t>542936; 627470</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>992066; 1098336</t>
+          <t>988394; 1099963</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1075363; 1183427</t>
+          <t>1069847; 1184093</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>329674; 465813</t>
+          <t>317457; 466090</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>873035; 977713</t>
+          <t>873730; 977973</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1061306; 1178750</t>
+          <t>1059267; 1179250</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1203999; 1316227</t>
+          <t>1198004; 1315886</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>518264; 809900</t>
+          <t>504971; 788405</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1429935; 1569869</t>
+          <t>1443179; 1577379</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2081858; 2243353</t>
+          <t>2087027; 2239782</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2308918; 2472259</t>
+          <t>2314822; 2470344</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>904865; 1231268</t>
+          <t>894116; 1219741</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P71_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P71_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,08; 17,47</t>
+          <t>12,08; 17,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,22; 31,92</t>
+          <t>25,0; 32,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,08; 38,8</t>
+          <t>30,96; 38,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,41; 14,6</t>
+          <t>10,66; 15,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,99; 27,27</t>
+          <t>20,69; 27,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,93; 34,16</t>
+          <t>26,91; 33,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,08; 38,38</t>
+          <t>30,8; 38,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,88; 17,84</t>
+          <t>14,91; 19,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,08; 21,31</t>
+          <t>17,27; 21,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,85; 31,86</t>
+          <t>26,99; 32,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,25; 37,58</t>
+          <t>32,09; 37,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,67; 15,5</t>
+          <t>13,59; 17,45</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,42; 19,38</t>
+          <t>14,3; 19,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,4; 38,52</t>
+          <t>32,31; 38,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,94; 37,36</t>
+          <t>30,81; 37,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,4</t>
+          <t>10,87; 15,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,37; 29,61</t>
+          <t>23,58; 29,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,42; 38,58</t>
+          <t>32,29; 38,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,93; 37,88</t>
+          <t>32,46; 38,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,2; 16,11</t>
+          <t>12,65; 16,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,65; 23,37</t>
+          <t>19,56; 23,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,52; 37,84</t>
+          <t>33,27; 37,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,36; 36,6</t>
+          <t>32,6; 36,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,66; 13,59</t>
+          <t>12,52; 15,4</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,47; 22,97</t>
+          <t>16,61; 23,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,93; 39,18</t>
+          <t>31,97; 39,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,54; 46,1</t>
+          <t>38,55; 45,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,91; 16,82</t>
+          <t>11,18; 17,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,24; 34,04</t>
+          <t>27,36; 34,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,43; 40,19</t>
+          <t>33,03; 40,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,96; 50,19</t>
+          <t>42,93; 50,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 18,03</t>
+          <t>14,92; 19,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,88; 27,69</t>
+          <t>22,76; 27,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33,39; 38,5</t>
+          <t>33,84; 38,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41,78; 47,39</t>
+          <t>41,99; 47,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,89; 16,05</t>
+          <t>13,83; 17,69</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,43; 23,8</t>
+          <t>18,46; 23,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,69; 26,16</t>
+          <t>20,8; 26,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,32; 28,0</t>
+          <t>21,95; 27,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,14; 17,3</t>
+          <t>13,99; 19,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,91; 32,75</t>
+          <t>27,34; 32,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,13; 27,45</t>
+          <t>22,13; 27,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,96; 31,81</t>
+          <t>26,09; 31,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,87; 39,24</t>
+          <t>16,6; 20,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,74; 27,48</t>
+          <t>23,85; 27,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,22; 26,09</t>
+          <t>22,13; 26,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,95; 28,85</t>
+          <t>24,93; 29,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,83; 29,43</t>
+          <t>16,04; 19,38</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,8; 19,42</t>
+          <t>16,71; 19,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,99; 32,27</t>
+          <t>29,01; 32,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,77; 35,16</t>
+          <t>31,84; 35,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,64</t>
+          <t>13,0; 15,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,36; 29,5</t>
+          <t>26,32; 29,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,9; 33,29</t>
+          <t>29,96; 33,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,97; 37,31</t>
+          <t>34,08; 37,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,86; 21,64</t>
+          <t>15,73; 18,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,05; 24,1</t>
+          <t>22,0; 24,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,02; 32,22</t>
+          <t>29,98; 32,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,58; 35,83</t>
+          <t>33,44; 35,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,67; 17,28</t>
+          <t>14,73; 16,53</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72479</t>
+          <t>88632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>108418</t>
+          <t>123263</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>180896</t>
+          <t>211895</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82842; 119751</t>
+          <t>82849; 119381</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>176615; 223530</t>
+          <t>175097; 225716</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>206811; 258133</t>
+          <t>206014; 255200</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58071; 90163</t>
+          <t>71696; 106642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>142535; 185126</t>
+          <t>140470; 186009</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>186372; 236414</t>
+          <t>186229; 234470</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>206678; 255170</t>
+          <t>204797; 253518</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84682; 127233</t>
+          <t>107490; 140416</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>233075; 290758</t>
+          <t>235617; 292206</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>373794; 443614</t>
+          <t>375864; 446157</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>429017; 499943</t>
+          <t>426902; 494618</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>155323; 206250</t>
+          <t>189366; 243158</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110600</t>
+          <t>137277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>133377</t>
+          <t>154389</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>243978</t>
+          <t>291665</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>136600; 183634</t>
+          <t>135501; 182970</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>328435; 390370</t>
+          <t>327452; 390675</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>313925; 378984</t>
+          <t>312588; 377085</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49142; 146534</t>
+          <t>112657; 164423</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>222076; 281405</t>
+          <t>224029; 280007</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>331956; 394949</t>
+          <t>330629; 393212</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>330549; 392066</t>
+          <t>335967; 396084</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>115969; 153218</t>
+          <t>134437; 178459</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>372894; 443565</t>
+          <t>371266; 445143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>682816; 770833</t>
+          <t>677763; 770871</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>663199; 750105</t>
+          <t>668277; 756450</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>163393; 289754</t>
+          <t>262785; 323269</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94741</t>
+          <t>110665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>117366</t>
+          <t>139805</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>212107</t>
+          <t>250470</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>110641; 154283</t>
+          <t>111596; 155899</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>240680; 295341</t>
+          <t>240957; 295478</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>290974; 348060</t>
+          <t>291104; 347067</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76375; 117753</t>
+          <t>88777; 135066</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>182234; 227707</t>
+          <t>183048; 229099</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>259068; 311437</t>
+          <t>255960; 313652</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>336772; 393484</t>
+          <t>336568; 393440</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>58466; 161549</t>
+          <t>120149; 159279</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>306722; 371239</t>
+          <t>305097; 368526</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>510449; 588563</t>
+          <t>517281; 591824</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>643005; 729322</t>
+          <t>646278; 724896</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>125974; 256120</t>
+          <t>221204; 283019</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136578</t>
+          <t>162165</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>248407</t>
+          <t>206123</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>384985</t>
+          <t>368289</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>170691; 220441</t>
+          <t>170973; 217708</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>194837; 246274</t>
+          <t>195797; 245562</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>208081; 261068</t>
+          <t>204650; 257704</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>111344; 158649</t>
+          <t>136833; 187657</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>273669; 333019</t>
+          <t>278025; 335016</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>232744; 288747</t>
+          <t>232821; 289687</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>270746; 331726</t>
+          <t>272052; 333425</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>182900; 425367</t>
+          <t>183956; 230857</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>461321; 533936</t>
+          <t>463418; 537936</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>442873; 520004</t>
+          <t>441226; 520429</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>492717; 569818</t>
+          <t>492426; 573071</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>316729; 589047</t>
+          <t>334558; 404231</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>414398</t>
+          <t>498739</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>607568</t>
+          <t>623580</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1021966</t>
+          <t>1122320</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>542936; 627470</t>
+          <t>539752; 628141</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>988394; 1099963</t>
+          <t>989070; 1096750</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1069847; 1184093</t>
+          <t>1072306; 1181665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>317457; 466090</t>
+          <t>452722; 545741</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>873730; 977973</t>
+          <t>872523; 974556</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1059267; 1179250</t>
+          <t>1061488; 1178397</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1198004; 1315886</t>
+          <t>1201964; 1319856</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>504971; 788405</t>
+          <t>581647; 665420</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1443179; 1577379</t>
+          <t>1440326; 1578494</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2087027; 2239782</t>
+          <t>2084308; 2246181</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2314822; 2470344</t>
+          <t>2305668; 2468465</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>894116; 1219741</t>
+          <t>1057634; 1186356</t>
         </is>
       </c>
     </row>
